--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
@@ -8,14 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include ValueSet #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:32:23+00:00</t>
+    <t>2026-09-16T15:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,11 +88,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes autorisés pour indiquer un acte.
+    <t>Codes autorisés par défaut pour indiquer un acte.
 Inclut :
-- Terminologie CCAM
-- NCIT (code C25218 : 'Intervention') si l'acte n'est pas trouvé dans CCAM
+- CCAM : terminologie facturante pour la production d'actes.
 - CISIS jdv-absent-or-unknown-procedure-cisis pour actes chirurgicaux inconnus ou absents.
+Deux additional bindings extensibles, portés par FRCoreProcedureProfile.code, complètent ce binding par défaut :
+- fr-core-vs-procedure-code-snomed (SNOMED CT) pour la demande d'acte ou de report d'actes à des fins internationales (en cours de validation en Europe).
+- fr-core-vs-procedure-code-autre (CISIS "Autre acte") si l'acte n'est pas trouvé dans CCAM ni SNOMED CT.
 Si aucun code approprié n'est disponible, l'acte peut être décrit en texte libre.</t>
   </si>
   <si>
@@ -124,19 +125,10 @@
     <t>https://smt.esante.gouv.fr/terminologie-ccam</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>C25218</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
     <t>ValueSet URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-procedure-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-procedure-cisis|20260716085852</t>
   </si>
 </sst>
 </file>
@@ -448,7 +440,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -459,54 +451,10 @@
       <c r="A1" t="s" s="1">
         <v>34</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>23</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:06:55+00:00</t>
+    <t>2026-09-16T15:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
 - CCAM : terminologie facturante pour la production d'actes.
 - CISIS jdv-absent-or-unknown-procedure-cisis pour actes chirurgicaux inconnus ou absents.
 Deux additional bindings extensibles, portés par FRCoreProcedureProfile.code, complètent ce binding par défaut :
-- fr-core-vs-procedure-code-snomed (SNOMED CT) pour la demande d'acte ou de report d'actes à des fins internationales (en cours de validation en Europe).
+- ValueSet IPS procedures-uv-ips (SNOMED CT, identique au parent EU Core) pour la demande d'acte ou de report d'actes à des fins internationales (en cours de validation en Europe).
 - fr-core-vs-procedure-code-autre (CISIS "Autre acte") si l'acte n'est pas trouvé dans CCAM ni SNOMED CT.
 Si aucun code approprié n'est disponible, l'acte peut être décrit en texte libre.</t>
   </si>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:10:32+00:00</t>
+    <t>2026-09-16T15:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-procedure-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:30:48+00:00</t>
+    <t>2026-09-17T13:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
